--- a/files/NBL_upcoming_projections_v4_shadow.xlsx
+++ b/files/NBL_upcoming_projections_v4_shadow.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS8"/>
+  <dimension ref="A1:AS7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -593,11 +593,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/matches/nz-breakers-v-cairns-taipans-men-30-09-2026</t>
+          <t>/matches/illawarra-hawks-v-adelaide-36ers-men-02-10-2026</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -610,89 +610,89 @@
         </is>
       </c>
       <c r="E2" s="2">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="F2" s="2">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>new zealand breakers</t>
+          <t>illawarra hawks</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cairns taipans</t>
+          <t>adelaide 36ers</t>
         </is>
       </c>
       <c r="I2">
-        <v>6.577816600263617</v>
+        <v>-1.335194534812118</v>
       </c>
       <c r="J2">
-        <v>5.169299288288808</v>
+        <v>-10.37261869423288</v>
       </c>
       <c r="K2">
-        <v>5.169299288288808</v>
+        <v>-10.37261869423288</v>
       </c>
       <c r="L2">
-        <v>-3.305954949435492</v>
+        <v>-3.87892859411747</v>
       </c>
       <c r="M2">
-        <v>-7.053837855463824</v>
+        <v>8.150041366571065</v>
       </c>
       <c r="N2">
-        <v>3.747882906028332</v>
+        <v>-12.02896996068853</v>
       </c>
       <c r="O2">
-        <v>-1.408517311974808</v>
+        <v>-9.037424159420762</v>
       </c>
       <c r="P2">
-        <v>-1.408517311974808</v>
+        <v>-9.037424159420762</v>
       </c>
       <c r="Q2">
         <v>0.2</v>
       </c>
       <c r="R2">
-        <v>0.05199528743618399</v>
+        <v>0.1147008321225729</v>
       </c>
       <c r="S2">
-        <v>184.3039845487071</v>
+        <v>189.5318882866171</v>
       </c>
       <c r="T2">
-        <v>94.18335039521669</v>
+        <v>86.56421220847052</v>
       </c>
       <c r="U2">
-        <v>88.65695989201535</v>
+        <v>95.10442961466767</v>
       </c>
       <c r="V2">
-        <v>182.8403102872321</v>
+        <v>181.6686418231382</v>
       </c>
       <c r="W2">
-        <v>-1.463674261475091</v>
+        <v>-7.86324646347893</v>
       </c>
       <c r="X2">
-        <v>-1.463674261475091</v>
+        <v>-7.86324646347893</v>
       </c>
       <c r="Y2">
         <v>0.3</v>
       </c>
       <c r="Z2">
-        <v>0.077992931154276</v>
+        <v>0.1720512481838594</v>
       </c>
       <c r="AA2">
-        <v>0.825997643718092</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AB2">
-        <v>0.825997643718092</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AC2">
-        <v>0.9455401546810884</v>
+        <v>0.8903358464701852</v>
       </c>
       <c r="AD2">
-        <v>0.825997643718092</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AE2">
-        <v>0.25997643718092</v>
+        <v>0.5735041606128645</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -714,42 +714,42 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick;Kael Robinson;Luke Paul</t>
+          <t>Dan Grida;Will Hickey;Amarco Doyle;John Jenkins III;Harvey White</t>
         </is>
       </c>
       <c r="AL2">
-        <v>6.504580337768646</v>
+        <v>-2.371794606142323</v>
       </c>
       <c r="AM2">
-        <v>-6.504580337768646</v>
+        <v>2.371794606142323</v>
       </c>
       <c r="AN2">
-        <v>184.1898283027996</v>
+        <v>188.1790069177983</v>
       </c>
       <c r="AO2">
-        <v>95.34720432028415</v>
+        <v>92.90360615582797</v>
       </c>
       <c r="AP2">
-        <v>88.84262398251549</v>
+        <v>95.27540076197029</v>
       </c>
       <c r="AQ2">
-        <v>0.7061074047156142</v>
+        <v>0.4216596318839952</v>
       </c>
       <c r="AR2">
-        <v>1.416215144214146</v>
+        <v>2.371581067725058</v>
       </c>
       <c r="AS2">
-        <v>3.402603590717717</v>
+        <v>1.729085595836218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/matches/sydney-kings-v-brisbane-bullets-men-30-09-2026</t>
+          <t>/matches/perth-wildcats-v-south-east-melbourne-phoenix-men-02-10-2026</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -762,89 +762,89 @@
         </is>
       </c>
       <c r="E3" s="2">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="F3" s="2">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sydney kings</t>
+          <t>perth wildcats</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>brisbane bullets</t>
+          <t>south east melbourne phoenix</t>
         </is>
       </c>
       <c r="I3">
-        <v>16.48241721398743</v>
+        <v>0.7026288772456866</v>
       </c>
       <c r="J3">
-        <v>8.793973294866079</v>
+        <v>5.845965126401673</v>
       </c>
       <c r="K3">
-        <v>8.793973294866079</v>
+        <v>5.845965126401673</v>
       </c>
       <c r="L3">
-        <v>11.57676238897146</v>
+        <v>-1.015980580062633</v>
       </c>
       <c r="M3">
-        <v>4.204205476365858</v>
+        <v>-5.205594440008651</v>
       </c>
       <c r="N3">
-        <v>7.372556912605602</v>
+        <v>4.189613859946018</v>
       </c>
       <c r="O3">
-        <v>-7.688443919121353</v>
+        <v>5.143336249155986</v>
       </c>
       <c r="P3">
-        <v>-7.688443919121353</v>
+        <v>5.143336249155986</v>
       </c>
       <c r="Q3">
         <v>0.2</v>
       </c>
       <c r="R3">
-        <v>0.06326291994699475</v>
+        <v>0.2</v>
       </c>
       <c r="S3">
-        <v>185.3442032290616</v>
+        <v>186.145844821383</v>
       </c>
       <c r="T3">
-        <v>101.519293408755</v>
+        <v>86.95055107347885</v>
       </c>
       <c r="U3">
-        <v>91.23779068924006</v>
+        <v>87.58246094005507</v>
       </c>
       <c r="V3">
-        <v>192.7570840979951</v>
+        <v>174.5330120135339</v>
       </c>
       <c r="W3">
-        <v>7.412880868933428</v>
+        <v>-11.61283280784906</v>
       </c>
       <c r="X3">
-        <v>7.412880868933428</v>
+        <v>-11.61283280784906</v>
       </c>
       <c r="Y3">
         <v>0.3</v>
       </c>
       <c r="Z3">
-        <v>0.09489437992049213</v>
+        <v>0.3</v>
       </c>
       <c r="AA3">
-        <v>0.8316314599734974</v>
+        <v>0.9496485891115073</v>
       </c>
       <c r="AB3">
-        <v>0.9464982351848411</v>
+        <v>0.9496485891115073</v>
       </c>
       <c r="AC3">
-        <v>0.8316314599734974</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>0.8316314599734974</v>
+        <v>0.9496485891115073</v>
       </c>
       <c r="AE3">
-        <v>0.3163145997349737</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -861,142 +861,142 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>league_last5;neutral_fallback</t>
+          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Lachlan Bofinger;Rio Bruton;Josh Duach;Billy McRae</t>
+          <t>Jo Lual-Acuil Jr.</t>
         </is>
       </c>
       <c r="AL3">
-        <v>15.9960238018151</v>
+        <v>1.731296127076884</v>
       </c>
       <c r="AM3">
-        <v>-15.9960238018151</v>
+        <v>-1.731296127076884</v>
       </c>
       <c r="AN3">
-        <v>186.0476439625436</v>
+        <v>182.6619949790283</v>
       </c>
       <c r="AO3">
-        <v>101.0218338821793</v>
+        <v>92.19664555305258</v>
       </c>
       <c r="AP3">
-        <v>85.02581008036424</v>
+        <v>90.46534942597569</v>
       </c>
       <c r="AQ3">
-        <v>0.9087344235551811</v>
+        <v>0.557358213146793</v>
       </c>
       <c r="AR3">
-        <v>1.100431516710643</v>
+        <v>1.794178279627553</v>
       </c>
       <c r="AS3">
-        <v>10.95703373554673</v>
+        <v>2.259163119481147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/matches/tasmania-jackjumpers-v-melbourne-united-men-01-10-2026</t>
+          <t>/matches/brisbane-bullets-v-tasmania-jackjumpers-men-03-10-2026</t>
         </is>
       </c>
       <c r="B4" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <v>46298</v>
+      </c>
+      <c r="F4" s="2">
         <v>46296</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E4" s="2">
-        <v>46296</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46292</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>brisbane bullets</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>tasmania jackjumpers</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>melbourne united</t>
-        </is>
-      </c>
       <c r="I4">
-        <v>-1.845764629053903</v>
+        <v>-4.892729581328908</v>
       </c>
       <c r="J4">
-        <v>-7.84064156666148</v>
+        <v>11.46109669507977</v>
       </c>
       <c r="K4">
-        <v>-7.84064156666148</v>
+        <v>11.46109669507977</v>
       </c>
       <c r="L4">
-        <v>-3.440783888326374</v>
+        <v>3.81750707863487</v>
       </c>
       <c r="M4">
-        <v>5.821355009040458</v>
+        <v>-5.976619827034386</v>
       </c>
       <c r="N4">
-        <v>-9.262138897366832</v>
+        <v>9.794126905669255</v>
       </c>
       <c r="O4">
-        <v>-5.994876937607577</v>
+        <v>16.35382627640868</v>
       </c>
       <c r="P4">
-        <v>-5.994876937607577</v>
+        <v>15</v>
       </c>
       <c r="Q4">
         <v>0.2</v>
       </c>
       <c r="R4">
-        <v>0.09703345255628018</v>
+        <v>0.0880190655015525</v>
       </c>
       <c r="S4">
-        <v>177.1327692540463</v>
+        <v>177.6573858471099</v>
       </c>
       <c r="T4">
-        <v>90.53312397844246</v>
+        <v>93.10222085897135</v>
       </c>
       <c r="U4">
-        <v>97.22570262643096</v>
+        <v>87.27444765667697</v>
       </c>
       <c r="V4">
-        <v>187.7588266048734</v>
+        <v>180.3766685156483</v>
       </c>
       <c r="W4">
-        <v>10.62605735082712</v>
+        <v>2.719282668538369</v>
       </c>
       <c r="X4">
-        <v>10.62605735082712</v>
+        <v>2.719282668538369</v>
       </c>
       <c r="Y4">
         <v>0.3</v>
       </c>
       <c r="Z4">
-        <v>0.1455501788344203</v>
+        <v>0.1320285982523288</v>
       </c>
       <c r="AA4">
-        <v>0.8485167262781401</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AB4">
-        <v>0.9558884344989201</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AC4">
-        <v>0.8485167262781401</v>
+        <v>0.9550161660653202</v>
       </c>
       <c r="AD4">
-        <v>0.8485167262781401</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AE4">
-        <v>0.4851672627814009</v>
+        <v>0.4400953275077625</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1013,47 +1013,47 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>league_last5_returning_conservative;league_last5;neutral_fallback</t>
+          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Nick Stoddart;Christian D'Angelo;Jai Fa'ale;Will Hynes</t>
+          <t>Rio Bruton;Josh Duach;Billy McRae;Nick Stoddart</t>
         </is>
       </c>
       <c r="AL4">
-        <v>-2.427468235959986</v>
+        <v>-3.57244359880562</v>
       </c>
       <c r="AM4">
-        <v>2.427468235959986</v>
+        <v>3.57244359880562</v>
       </c>
       <c r="AN4">
-        <v>178.679393801764</v>
+        <v>178.0164089260889</v>
       </c>
       <c r="AO4">
-        <v>88.12596278290201</v>
+        <v>87.22198266364164</v>
       </c>
       <c r="AP4">
-        <v>90.553431018862</v>
+        <v>90.79442626244726</v>
       </c>
       <c r="AQ4">
-        <v>0.4198453917864801</v>
+        <v>0.3829646850905365</v>
       </c>
       <c r="AR4">
-        <v>2.381829167505947</v>
+        <v>2.611206826456049</v>
       </c>
       <c r="AS4">
-        <v>1.723678457160441</v>
+        <v>1.620652782485762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/matches/illawarra-hawks-v-adelaide-36ers-men-02-10-2026</t>
+          <t>/matches/melbourne-united-v-cairns-taipans-men-03-10-2026</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,89 +1066,89 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" s="2">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>illawarra hawks</t>
+          <t>melbourne united</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>adelaide 36ers</t>
+          <t>cairns taipans</t>
         </is>
       </c>
       <c r="I5">
-        <v>-1.52198022214499</v>
+        <v>8.873042196210363</v>
       </c>
       <c r="J5">
-        <v>-11.41119535533512</v>
+        <v>10.62336920890479</v>
       </c>
       <c r="K5">
-        <v>-11.41119535533512</v>
+        <v>10.62336920890479</v>
       </c>
       <c r="L5">
-        <v>-4.514528044725636</v>
+        <v>2.57555777695428</v>
       </c>
       <c r="M5">
-        <v>8.318245671589439</v>
+        <v>-6.380841642539997</v>
       </c>
       <c r="N5">
-        <v>-12.83277371631507</v>
+        <v>8.956399419494277</v>
       </c>
       <c r="O5">
-        <v>-9.889215133190131</v>
+        <v>1.750327012694431</v>
       </c>
       <c r="P5">
-        <v>-9.889215133190131</v>
+        <v>1.750327012694431</v>
       </c>
       <c r="Q5">
         <v>0.2</v>
       </c>
       <c r="R5">
-        <v>0.1147008321225729</v>
+        <v>0.1831611045231239</v>
       </c>
       <c r="S5">
-        <v>189.2285811048577</v>
+        <v>176.2359142406692</v>
       </c>
       <c r="T5">
-        <v>86.40387178816283</v>
+        <v>95.1348129111047</v>
       </c>
       <c r="U5">
-        <v>95.01608183335041</v>
+        <v>85.04250781679859</v>
       </c>
       <c r="V5">
-        <v>181.4199536215132</v>
+        <v>180.1773207279033</v>
       </c>
       <c r="W5">
-        <v>-7.80862748334448</v>
+        <v>3.941406487234076</v>
       </c>
       <c r="X5">
-        <v>-7.80862748334448</v>
+        <v>3.941406487234076</v>
       </c>
       <c r="Y5">
         <v>0.3</v>
       </c>
       <c r="Z5">
-        <v>0.1720512481838594</v>
+        <v>0.2747416567846859</v>
       </c>
       <c r="AA5">
-        <v>0.8573504160612865</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AB5">
-        <v>0.8573504160612865</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AC5">
-        <v>0.8903358464701852</v>
+        <v>0.9468918844160874</v>
       </c>
       <c r="AD5">
-        <v>0.8573504160612865</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AE5">
-        <v>0.5735041606128645</v>
+        <v>0.9158055226156194</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1165,47 +1165,47 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Dan Grida;Will Hickey;Amarco Doyle;John Jenkins III;Harvey White</t>
+          <t>Jai Fa'ale;Will Hynes;Luke Paul</t>
         </is>
       </c>
       <c r="AL5">
-        <v>-2.656281426961038</v>
+        <v>9.193634025132136</v>
       </c>
       <c r="AM5">
-        <v>2.656281426961038</v>
+        <v>-9.193634025132136</v>
       </c>
       <c r="AN5">
-        <v>187.8850969997455</v>
+        <v>177.3187827890338</v>
       </c>
       <c r="AO5">
-        <v>92.61440778639223</v>
+        <v>93.25620840708297</v>
       </c>
       <c r="AP5">
-        <v>95.27068921335328</v>
+        <v>84.06257438195084</v>
       </c>
       <c r="AQ5">
-        <v>0.4124073189536496</v>
+        <v>0.7782023579944195</v>
       </c>
       <c r="AR5">
-        <v>2.424787228648553</v>
+        <v>1.285012811548395</v>
       </c>
       <c r="AS5">
-        <v>1.701859182825864</v>
+        <v>4.508614207786932</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/matches/perth-wildcats-v-south-east-melbourne-phoenix-men-02-10-2026</t>
+          <t>/matches/adelaide-36ers-v-nz-breakers-men-04-10-2026</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,89 +1218,89 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="F6" s="2">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>perth wildcats</t>
+          <t>adelaide 36ers</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>south east melbourne phoenix</t>
+          <t>new zealand breakers</t>
         </is>
       </c>
       <c r="I6">
-        <v>0.7712344269142477</v>
+        <v>1.11091053240331</v>
       </c>
       <c r="J6">
-        <v>5.968882729806214</v>
+        <v>10.21768672024316</v>
       </c>
       <c r="K6">
-        <v>5.968882729806214</v>
+        <v>10.21768672024316</v>
       </c>
       <c r="L6">
-        <v>-1.405765446037439</v>
+        <v>7.72462376534731</v>
       </c>
       <c r="M6">
-        <v>-5.953069814863699</v>
+        <v>-0.8242020544248913</v>
       </c>
       <c r="N6">
-        <v>4.547304368826261</v>
+        <v>8.548825819772201</v>
       </c>
       <c r="O6">
-        <v>5.197648302891967</v>
+        <v>9.106776187839849</v>
       </c>
       <c r="P6">
-        <v>5.197648302891967</v>
+        <v>9.106776187839849</v>
       </c>
       <c r="Q6">
         <v>0.2</v>
       </c>
       <c r="R6">
-        <v>0.2</v>
+        <v>0.1104751692245827</v>
       </c>
       <c r="S6">
-        <v>185.9341225353442</v>
+        <v>187.7010393664982</v>
       </c>
       <c r="T6">
-        <v>86.96055854404889</v>
+        <v>96.26215855282854</v>
       </c>
       <c r="U6">
-        <v>87.08915076072726</v>
+        <v>90.79262213091847</v>
       </c>
       <c r="V6">
-        <v>174.0497093047762</v>
+        <v>187.054780683747</v>
       </c>
       <c r="W6">
-        <v>-11.88441323056799</v>
+        <v>-0.6462586827511814</v>
       </c>
       <c r="X6">
-        <v>-11.88441323056799</v>
+        <v>-0.6462586827511814</v>
       </c>
       <c r="Y6">
         <v>0.3</v>
       </c>
       <c r="Z6">
-        <v>0.3</v>
+        <v>0.1657127538368741</v>
       </c>
       <c r="AA6">
-        <v>0.9041246379706382</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AB6">
-        <v>0.9041246379706382</v>
+        <v>0.8903358464701852</v>
       </c>
       <c r="AC6">
-        <v>1</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AD6">
-        <v>0.9041246379706382</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>0.5523758461229135</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1322,42 +1322,42 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Jo Lual-Acuil Jr.;Brandon Knight</t>
+          <t>John Jenkins III;Harvey White;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
         </is>
       </c>
       <c r="AL6">
-        <v>1.810764087492641</v>
+        <v>2.116983172845317</v>
       </c>
       <c r="AM6">
-        <v>-1.810764087492641</v>
+        <v>-2.116983172845317</v>
       </c>
       <c r="AN6">
-        <v>182.3687985661738</v>
+        <v>187.5939460604885</v>
       </c>
       <c r="AO6">
-        <v>92.08978132683319</v>
+        <v>94.85546461666692</v>
       </c>
       <c r="AP6">
-        <v>90.27901723934056</v>
+        <v>92.7384814438216</v>
       </c>
       <c r="AQ6">
-        <v>0.559971519354348</v>
+        <v>0.5700161432638842</v>
       </c>
       <c r="AR6">
-        <v>1.785805108718759</v>
+        <v>1.754336279449999</v>
       </c>
       <c r="AS6">
-        <v>2.272580171475955</v>
+        <v>2.325668706706138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/matches/brisbane-bullets-v-tasmania-jackjumpers-men-03-10-2026</t>
+          <t>/matches/south-east-melbourne-phoenix-v-illawarra-hawks-men-04-10-2026</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,89 +1370,89 @@
         </is>
       </c>
       <c r="E7" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" s="2">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>brisbane bullets</t>
+          <t>south east melbourne phoenix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tasmania jackjumpers</t>
+          <t>illawarra hawks</t>
         </is>
       </c>
       <c r="I7">
-        <v>-4.912249563142566</v>
+        <v>4.614123382190286</v>
       </c>
       <c r="J7">
-        <v>9.063164391847845</v>
+        <v>0.4105067446507376</v>
       </c>
       <c r="K7">
-        <v>9.063164391847845</v>
+        <v>0.4105067446507376</v>
       </c>
       <c r="L7">
-        <v>4.198854772123268</v>
+        <v>-5.143505324296937</v>
       </c>
       <c r="M7">
-        <v>-3.446730672650893</v>
+        <v>-3.885151168476717</v>
       </c>
       <c r="N7">
-        <v>7.645585444774161</v>
+        <v>-1.25835415582022</v>
       </c>
       <c r="O7">
-        <v>13.97541395499041</v>
+        <v>-4.203616637539549</v>
       </c>
       <c r="P7">
-        <v>13.97541395499041</v>
+        <v>-4.203616637539549</v>
       </c>
       <c r="Q7">
         <v>0.2</v>
       </c>
       <c r="R7">
-        <v>0.06326291994699475</v>
+        <v>0.1147008321225729</v>
       </c>
       <c r="S7">
-        <v>178.9335838026616</v>
+        <v>189.6986029213629</v>
       </c>
       <c r="T7">
-        <v>91.95101306062534</v>
+        <v>86.52956592639438</v>
       </c>
       <c r="U7">
-        <v>88.91468194239923</v>
+        <v>86.87030465523057</v>
       </c>
       <c r="V7">
-        <v>180.8656950030246</v>
+        <v>173.399870581625</v>
       </c>
       <c r="W7">
-        <v>1.932111200362925</v>
+        <v>-16.29873233973797</v>
       </c>
       <c r="X7">
-        <v>1.932111200362925</v>
+        <v>-16.29873233973797</v>
       </c>
       <c r="Y7">
         <v>0.3</v>
       </c>
       <c r="Z7">
-        <v>0.09489437992049213</v>
+        <v>0.1720512481838594</v>
       </c>
       <c r="AA7">
-        <v>0.8316314599734974</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AB7">
-        <v>0.8316314599734974</v>
+        <v>1</v>
       </c>
       <c r="AC7">
-        <v>0.9558884344989201</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AD7">
-        <v>0.8316314599734974</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AE7">
-        <v>0.3163145997349737</v>
+        <v>0.5735041606128645</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1469,189 +1469,37 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Rio Bruton;Josh Duach;Billy McRae;Nick Stoddart</t>
+          <t>Dan Grida;Will Hickey;Amarco Doyle</t>
         </is>
       </c>
       <c r="AL7">
-        <v>-4.028124068881895</v>
+        <v>4.131965055940208</v>
       </c>
       <c r="AM7">
-        <v>4.028124068881895</v>
+        <v>-4.131965055940208</v>
       </c>
       <c r="AN7">
-        <v>179.1169302969575</v>
+        <v>186.8943856784964</v>
       </c>
       <c r="AO7">
-        <v>87.54440311403781</v>
+        <v>95.5131753672183</v>
       </c>
       <c r="AP7">
-        <v>91.57252718291971</v>
+        <v>91.38121031127808</v>
       </c>
       <c r="AQ7">
-        <v>0.3685572237252813</v>
+        <v>0.6347010957155231</v>
       </c>
       <c r="AR7">
-        <v>2.713282865255653</v>
+        <v>1.575544782812548</v>
       </c>
       <c r="AS7">
-        <v>1.583674780317599</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>/matches/melbourne-united-v-cairns-taipans-men-03-10-2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <v>46298</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E8" s="2">
-        <v>46298</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46292</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>melbourne united</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>cairns taipans</t>
-        </is>
-      </c>
-      <c r="I8">
-        <v>8.343997864505027</v>
-      </c>
-      <c r="J8">
-        <v>14.1719876854107</v>
-      </c>
-      <c r="K8">
-        <v>14.1719876854107</v>
-      </c>
-      <c r="L8">
-        <v>5.737433610800474</v>
-      </c>
-      <c r="M8">
-        <v>-7.016975127536545</v>
-      </c>
-      <c r="N8">
-        <v>12.75440873833702</v>
-      </c>
-      <c r="O8">
-        <v>5.827989820905676</v>
-      </c>
-      <c r="P8">
-        <v>5.827989820905676</v>
-      </c>
-      <c r="Q8">
-        <v>0.2</v>
-      </c>
-      <c r="R8">
-        <v>0.09703345255628018</v>
-      </c>
-      <c r="S8">
-        <v>177.2076059226553</v>
-      </c>
-      <c r="T8">
-        <v>98.59475540510167</v>
-      </c>
-      <c r="U8">
-        <v>86.5440201583141</v>
-      </c>
-      <c r="V8">
-        <v>185.1387755634158</v>
-      </c>
-      <c r="W8">
-        <v>7.931169640760515</v>
-      </c>
-      <c r="X8">
-        <v>7.931169640760515</v>
-      </c>
-      <c r="Y8">
-        <v>0.3</v>
-      </c>
-      <c r="Z8">
-        <v>0.1455501788344203</v>
-      </c>
-      <c r="AA8">
-        <v>0.8485167262781401</v>
-      </c>
-      <c r="AB8">
-        <v>0.8485167262781401</v>
-      </c>
-      <c r="AC8">
-        <v>0.9455401546810884</v>
-      </c>
-      <c r="AD8">
-        <v>0.8485167262781401</v>
-      </c>
-      <c r="AE8">
-        <v>0.4851672627814009</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>true_home</t>
-        </is>
-      </c>
-      <c r="AG8">
-        <v>1.047658555274772</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>named_modelled_minutes/named_modelled_minutes</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Christian D'Angelo;Jai Fa'ale;Will Hynes;Luke Paul</t>
-        </is>
-      </c>
-      <c r="AL8">
-        <v>8.909507838290363</v>
-      </c>
-      <c r="AM8">
-        <v>-8.909507838290363</v>
-      </c>
-      <c r="AN8">
-        <v>178.3619890822341</v>
-      </c>
-      <c r="AO8">
-        <v>93.63574846026222</v>
-      </c>
-      <c r="AP8">
-        <v>84.72624062197187</v>
-      </c>
-      <c r="AQ8">
-        <v>0.7710953538993635</v>
-      </c>
-      <c r="AR8">
-        <v>1.296856471697158</v>
-      </c>
-      <c r="AS8">
-        <v>4.368631292701486</v>
+        <v>2.73748425815493</v>
       </c>
     </row>
   </sheetData>

--- a/files/NBL_upcoming_projections_v4_shadow.xlsx
+++ b/files/NBL_upcoming_projections_v4_shadow.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS7"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -593,11 +593,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/matches/illawarra-hawks-v-adelaide-36ers-men-02-10-2026</t>
+          <t>/matches/brisbane-bullets-v-tasmania-jackjumpers-men-03-10-2026</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -610,89 +610,89 @@
         </is>
       </c>
       <c r="E2" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" s="2">
         <v>46296</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>illawarra hawks</t>
+          <t>brisbane bullets</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>adelaide 36ers</t>
+          <t>tasmania jackjumpers</t>
         </is>
       </c>
       <c r="I2">
-        <v>-1.335194534812118</v>
+        <v>-4.892729581328908</v>
       </c>
       <c r="J2">
-        <v>-10.37261869423288</v>
+        <v>11.46109669507977</v>
       </c>
       <c r="K2">
-        <v>-10.37261869423288</v>
+        <v>11.46109669507977</v>
       </c>
       <c r="L2">
-        <v>-3.87892859411747</v>
+        <v>3.81750707863487</v>
       </c>
       <c r="M2">
-        <v>8.150041366571065</v>
+        <v>-5.976619827034386</v>
       </c>
       <c r="N2">
-        <v>-12.02896996068853</v>
+        <v>9.794126905669255</v>
       </c>
       <c r="O2">
-        <v>-9.037424159420762</v>
+        <v>16.35382627640868</v>
       </c>
       <c r="P2">
-        <v>-9.037424159420762</v>
+        <v>15</v>
       </c>
       <c r="Q2">
         <v>0.2</v>
       </c>
       <c r="R2">
-        <v>0.1147008321225729</v>
+        <v>0.0880190655015525</v>
       </c>
       <c r="S2">
-        <v>189.5318882866171</v>
+        <v>177.6573858471099</v>
       </c>
       <c r="T2">
-        <v>86.56421220847052</v>
+        <v>93.10222085897135</v>
       </c>
       <c r="U2">
-        <v>95.10442961466767</v>
+        <v>87.27444765667697</v>
       </c>
       <c r="V2">
-        <v>181.6686418231382</v>
+        <v>180.3766685156483</v>
       </c>
       <c r="W2">
-        <v>-7.86324646347893</v>
+        <v>2.719282668538369</v>
       </c>
       <c r="X2">
-        <v>-7.86324646347893</v>
+        <v>2.719282668538369</v>
       </c>
       <c r="Y2">
         <v>0.3</v>
       </c>
       <c r="Z2">
-        <v>0.1720512481838594</v>
+        <v>0.1320285982523288</v>
       </c>
       <c r="AA2">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AB2">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AC2">
-        <v>0.8903358464701852</v>
+        <v>0.9550161660653202</v>
       </c>
       <c r="AD2">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AE2">
-        <v>0.5735041606128645</v>
+        <v>0.4400953275077625</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -714,42 +714,42 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Dan Grida;Will Hickey;Amarco Doyle;John Jenkins III;Harvey White</t>
+          <t>Rio Bruton;Josh Duach;Billy McRae;Nick Stoddart</t>
         </is>
       </c>
       <c r="AL2">
-        <v>-2.371794606142323</v>
+        <v>-3.57244359880562</v>
       </c>
       <c r="AM2">
-        <v>2.371794606142323</v>
+        <v>3.57244359880562</v>
       </c>
       <c r="AN2">
-        <v>188.1790069177983</v>
+        <v>178.0164089260889</v>
       </c>
       <c r="AO2">
-        <v>92.90360615582797</v>
+        <v>87.22198266364164</v>
       </c>
       <c r="AP2">
-        <v>95.27540076197029</v>
+        <v>90.79442626244726</v>
       </c>
       <c r="AQ2">
-        <v>0.4216596318839952</v>
+        <v>0.3829646850905365</v>
       </c>
       <c r="AR2">
-        <v>2.371581067725058</v>
+        <v>2.611206826456049</v>
       </c>
       <c r="AS2">
-        <v>1.729085595836218</v>
+        <v>1.620652782485762</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/matches/perth-wildcats-v-south-east-melbourne-phoenix-men-02-10-2026</t>
+          <t>/matches/melbourne-united-v-cairns-taipans-men-03-10-2026</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -762,89 +762,89 @@
         </is>
       </c>
       <c r="E3" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" s="2">
         <v>46296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>perth wildcats</t>
+          <t>melbourne united</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>south east melbourne phoenix</t>
+          <t>cairns taipans</t>
         </is>
       </c>
       <c r="I3">
-        <v>0.7026288772456866</v>
+        <v>8.873042196210363</v>
       </c>
       <c r="J3">
-        <v>5.845965126401673</v>
+        <v>11.50063075049427</v>
       </c>
       <c r="K3">
-        <v>5.845965126401673</v>
+        <v>11.50063075049427</v>
       </c>
       <c r="L3">
-        <v>-1.015980580062633</v>
+        <v>2.57555777695428</v>
       </c>
       <c r="M3">
-        <v>-5.205594440008651</v>
+        <v>-7.25810318412947</v>
       </c>
       <c r="N3">
-        <v>4.189613859946018</v>
+        <v>9.833660961083751</v>
       </c>
       <c r="O3">
-        <v>5.143336249155986</v>
+        <v>2.627588554283903</v>
       </c>
       <c r="P3">
-        <v>5.143336249155986</v>
+        <v>2.627588554283903</v>
       </c>
       <c r="Q3">
         <v>0.2</v>
       </c>
       <c r="R3">
-        <v>0.2</v>
+        <v>0.1831611045231239</v>
       </c>
       <c r="S3">
-        <v>186.145844821383</v>
+        <v>176.2359142406692</v>
       </c>
       <c r="T3">
-        <v>86.95055107347885</v>
+        <v>94.51175139949508</v>
       </c>
       <c r="U3">
-        <v>87.58246094005507</v>
+        <v>84.4885972531078</v>
       </c>
       <c r="V3">
-        <v>174.5330120135339</v>
+        <v>179.0003486526029</v>
       </c>
       <c r="W3">
-        <v>-11.61283280784906</v>
+        <v>2.764434411933678</v>
       </c>
       <c r="X3">
-        <v>-11.61283280784906</v>
+        <v>2.764434411933678</v>
       </c>
       <c r="Y3">
         <v>0.3</v>
       </c>
       <c r="Z3">
-        <v>0.3</v>
+        <v>0.2747416567846859</v>
       </c>
       <c r="AA3">
-        <v>0.9496485891115073</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AB3">
-        <v>0.9496485891115073</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AC3">
         <v>1</v>
       </c>
       <c r="AD3">
-        <v>0.9496485891115073</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0.9158055226156194</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -861,47 +861,47 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Jo Lual-Acuil Jr.</t>
+          <t>Jai Fa'ale;Will Hynes</t>
         </is>
       </c>
       <c r="AL3">
-        <v>1.731296127076884</v>
+        <v>9.354314218045321</v>
       </c>
       <c r="AM3">
-        <v>-1.731296127076884</v>
+        <v>-9.354314218045321</v>
       </c>
       <c r="AN3">
-        <v>182.6619949790283</v>
+        <v>176.9954195310765</v>
       </c>
       <c r="AO3">
-        <v>92.19664555305258</v>
+        <v>93.17486687456089</v>
       </c>
       <c r="AP3">
-        <v>90.46534942597569</v>
+        <v>83.82055265651557</v>
       </c>
       <c r="AQ3">
-        <v>0.557358213146793</v>
+        <v>0.7821650904627131</v>
       </c>
       <c r="AR3">
-        <v>1.794178279627553</v>
+        <v>1.278502469866585</v>
       </c>
       <c r="AS3">
-        <v>2.259163119481147</v>
+        <v>4.590632429504278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/matches/brisbane-bullets-v-tasmania-jackjumpers-men-03-10-2026</t>
+          <t>/matches/adelaide-36ers-v-nz-breakers-men-04-10-2026</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,89 +914,89 @@
         </is>
       </c>
       <c r="E4" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" s="2">
         <v>46296</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>brisbane bullets</t>
+          <t>adelaide 36ers</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tasmania jackjumpers</t>
+          <t>new zealand breakers</t>
         </is>
       </c>
       <c r="I4">
-        <v>-4.892729581328908</v>
+        <v>1.11091053240331</v>
       </c>
       <c r="J4">
-        <v>11.46109669507977</v>
+        <v>10.21768672024316</v>
       </c>
       <c r="K4">
-        <v>11.46109669507977</v>
+        <v>10.21768672024316</v>
       </c>
       <c r="L4">
-        <v>3.81750707863487</v>
+        <v>7.72462376534731</v>
       </c>
       <c r="M4">
-        <v>-5.976619827034386</v>
+        <v>-0.8242020544248913</v>
       </c>
       <c r="N4">
-        <v>9.794126905669255</v>
+        <v>8.548825819772201</v>
       </c>
       <c r="O4">
-        <v>16.35382627640868</v>
+        <v>9.106776187839849</v>
       </c>
       <c r="P4">
-        <v>15</v>
+        <v>9.106776187839849</v>
       </c>
       <c r="Q4">
         <v>0.2</v>
       </c>
       <c r="R4">
-        <v>0.0880190655015525</v>
+        <v>0.1104751692245827</v>
       </c>
       <c r="S4">
-        <v>177.6573858471099</v>
+        <v>187.7010393664982</v>
       </c>
       <c r="T4">
-        <v>93.10222085897135</v>
+        <v>96.26215855282854</v>
       </c>
       <c r="U4">
-        <v>87.27444765667697</v>
+        <v>90.79262213091847</v>
       </c>
       <c r="V4">
-        <v>180.3766685156483</v>
+        <v>187.054780683747</v>
       </c>
       <c r="W4">
-        <v>2.719282668538369</v>
+        <v>-0.6462586827511814</v>
       </c>
       <c r="X4">
-        <v>2.719282668538369</v>
+        <v>-0.6462586827511814</v>
       </c>
       <c r="Y4">
         <v>0.3</v>
       </c>
       <c r="Z4">
-        <v>0.1320285982523288</v>
+        <v>0.1657127538368741</v>
       </c>
       <c r="AA4">
-        <v>0.8440095327507763</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AB4">
-        <v>0.8440095327507763</v>
+        <v>0.8903358464701852</v>
       </c>
       <c r="AC4">
-        <v>0.9550161660653202</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AD4">
-        <v>0.8440095327507763</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AE4">
-        <v>0.4400953275077625</v>
+        <v>0.5523758461229135</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1018,42 +1018,42 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Rio Bruton;Josh Duach;Billy McRae;Nick Stoddart</t>
+          <t>John Jenkins III;Harvey White;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
         </is>
       </c>
       <c r="AL4">
-        <v>-3.57244359880562</v>
+        <v>2.116983172845317</v>
       </c>
       <c r="AM4">
-        <v>3.57244359880562</v>
+        <v>-2.116983172845317</v>
       </c>
       <c r="AN4">
-        <v>178.0164089260889</v>
+        <v>187.5939460604885</v>
       </c>
       <c r="AO4">
-        <v>87.22198266364164</v>
+        <v>94.85546461666692</v>
       </c>
       <c r="AP4">
-        <v>90.79442626244726</v>
+        <v>92.7384814438216</v>
       </c>
       <c r="AQ4">
-        <v>0.3829646850905365</v>
+        <v>0.5700161432638842</v>
       </c>
       <c r="AR4">
-        <v>2.611206826456049</v>
+        <v>1.754336279449999</v>
       </c>
       <c r="AS4">
-        <v>1.620652782485762</v>
+        <v>2.325668706706138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/matches/melbourne-united-v-cairns-taipans-men-03-10-2026</t>
+          <t>/matches/south-east-melbourne-phoenix-v-illawarra-hawks-men-04-10-2026</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,89 +1066,89 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" s="2">
         <v>46296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>melbourne united</t>
+          <t>south east melbourne phoenix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cairns taipans</t>
+          <t>illawarra hawks</t>
         </is>
       </c>
       <c r="I5">
-        <v>8.873042196210363</v>
+        <v>4.614123382190286</v>
       </c>
       <c r="J5">
-        <v>10.62336920890479</v>
+        <v>0.4105067446507376</v>
       </c>
       <c r="K5">
-        <v>10.62336920890479</v>
+        <v>0.4105067446507376</v>
       </c>
       <c r="L5">
-        <v>2.57555777695428</v>
+        <v>-5.143505324296937</v>
       </c>
       <c r="M5">
-        <v>-6.380841642539997</v>
+        <v>-3.885151168476717</v>
       </c>
       <c r="N5">
-        <v>8.956399419494277</v>
+        <v>-1.25835415582022</v>
       </c>
       <c r="O5">
-        <v>1.750327012694431</v>
+        <v>-4.203616637539549</v>
       </c>
       <c r="P5">
-        <v>1.750327012694431</v>
+        <v>-4.203616637539549</v>
       </c>
       <c r="Q5">
         <v>0.2</v>
       </c>
       <c r="R5">
-        <v>0.1831611045231239</v>
+        <v>0.1147008321225729</v>
       </c>
       <c r="S5">
-        <v>176.2359142406692</v>
+        <v>189.6986029213629</v>
       </c>
       <c r="T5">
-        <v>95.1348129111047</v>
+        <v>86.52956592639438</v>
       </c>
       <c r="U5">
-        <v>85.04250781679859</v>
+        <v>86.87030465523057</v>
       </c>
       <c r="V5">
-        <v>180.1773207279033</v>
+        <v>173.399870581625</v>
       </c>
       <c r="W5">
-        <v>3.941406487234076</v>
+        <v>-16.29873233973797</v>
       </c>
       <c r="X5">
-        <v>3.941406487234076</v>
+        <v>-16.29873233973797</v>
       </c>
       <c r="Y5">
         <v>0.3</v>
       </c>
       <c r="Z5">
-        <v>0.2747416567846859</v>
+        <v>0.1720512481838594</v>
       </c>
       <c r="AA5">
-        <v>0.891580552261562</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AB5">
-        <v>0.891580552261562</v>
+        <v>1</v>
       </c>
       <c r="AC5">
-        <v>0.9468918844160874</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AD5">
-        <v>0.891580552261562</v>
+        <v>0.8573504160612865</v>
       </c>
       <c r="AE5">
-        <v>0.9158055226156194</v>
+        <v>0.5735041606128645</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1170,42 +1170,42 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Jai Fa'ale;Will Hynes;Luke Paul</t>
+          <t>Dan Grida;Will Hickey;Amarco Doyle</t>
         </is>
       </c>
       <c r="AL5">
-        <v>9.193634025132136</v>
+        <v>4.131965055940208</v>
       </c>
       <c r="AM5">
-        <v>-9.193634025132136</v>
+        <v>-4.131965055940208</v>
       </c>
       <c r="AN5">
-        <v>177.3187827890338</v>
+        <v>186.8943856784964</v>
       </c>
       <c r="AO5">
-        <v>93.25620840708297</v>
+        <v>95.5131753672183</v>
       </c>
       <c r="AP5">
-        <v>84.06257438195084</v>
+        <v>91.38121031127808</v>
       </c>
       <c r="AQ5">
-        <v>0.7782023579944195</v>
+        <v>0.6347010957155231</v>
       </c>
       <c r="AR5">
-        <v>1.285012811548395</v>
+        <v>1.575544782812548</v>
       </c>
       <c r="AS5">
-        <v>4.508614207786932</v>
+        <v>2.73748425815493</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/matches/adelaide-36ers-v-nz-breakers-men-04-10-2026</t>
+          <t>/matches/adelaide-36ers-v-melbourne-united-men-07-10-2026</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="F6" s="2">
         <v>46296</v>
@@ -1230,77 +1230,77 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>new zealand breakers</t>
+          <t>melbourne united</t>
         </is>
       </c>
       <c r="I6">
-        <v>1.11091053240331</v>
+        <v>0.4771933121615604</v>
       </c>
       <c r="J6">
-        <v>10.21768672024316</v>
+        <v>6.982526168355089</v>
       </c>
       <c r="K6">
-        <v>10.21768672024316</v>
+        <v>6.982526168355089</v>
       </c>
       <c r="L6">
-        <v>7.72462376534731</v>
+        <v>7.773458410712558</v>
       </c>
       <c r="M6">
-        <v>-0.8242020544248913</v>
+        <v>2.482858807531738</v>
       </c>
       <c r="N6">
-        <v>8.548825819772201</v>
+        <v>5.290599603180819</v>
       </c>
       <c r="O6">
-        <v>9.106776187839849</v>
+        <v>6.505332856193529</v>
       </c>
       <c r="P6">
-        <v>9.106776187839849</v>
+        <v>6.505332856193529</v>
       </c>
       <c r="Q6">
         <v>0.2</v>
       </c>
       <c r="R6">
-        <v>0.1104751692245827</v>
+        <v>0.1806716929403703</v>
       </c>
       <c r="S6">
-        <v>187.7010393664982</v>
+        <v>180.4772482411747</v>
       </c>
       <c r="T6">
-        <v>96.26215855282854</v>
+        <v>94.76342739130703</v>
       </c>
       <c r="U6">
-        <v>90.79262213091847</v>
+        <v>92.38807047670807</v>
       </c>
       <c r="V6">
-        <v>187.054780683747</v>
+        <v>187.1514978680151</v>
       </c>
       <c r="W6">
-        <v>-0.6462586827511814</v>
+        <v>6.674249626840435</v>
       </c>
       <c r="X6">
-        <v>-0.6462586827511814</v>
+        <v>6.674249626840435</v>
       </c>
       <c r="Y6">
         <v>0.3</v>
       </c>
       <c r="Z6">
-        <v>0.1657127538368741</v>
+        <v>0.2710075394105554</v>
       </c>
       <c r="AA6">
-        <v>0.8552375846122914</v>
+        <v>0.8903358464701852</v>
       </c>
       <c r="AB6">
         <v>0.8903358464701852</v>
       </c>
       <c r="AC6">
-        <v>0.8552375846122914</v>
+        <v>0.891580552261562</v>
       </c>
       <c r="AD6">
-        <v>0.8552375846122914</v>
+        <v>0.8903358464701852</v>
       </c>
       <c r="AE6">
-        <v>0.5523758461229135</v>
+        <v>0.9033584647018513</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1322,42 +1322,42 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>John Jenkins III;Harvey White;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
+          <t>John Jenkins III;Harvey White;Jai Fa'ale;Will Hynes</t>
         </is>
       </c>
       <c r="AL6">
-        <v>2.116983172845317</v>
+        <v>1.652522812430659</v>
       </c>
       <c r="AM6">
-        <v>-2.116983172845317</v>
+        <v>-1.652522812430659</v>
       </c>
       <c r="AN6">
-        <v>187.5939460604885</v>
+        <v>182.2860202099565</v>
       </c>
       <c r="AO6">
-        <v>94.85546461666692</v>
+        <v>91.96927151119358</v>
       </c>
       <c r="AP6">
-        <v>92.7384814438216</v>
+        <v>90.31674869876294</v>
       </c>
       <c r="AQ6">
-        <v>0.5700161432638842</v>
+        <v>0.5547652846938359</v>
       </c>
       <c r="AR6">
-        <v>1.754336279449999</v>
+        <v>1.802564125027903</v>
       </c>
       <c r="AS6">
-        <v>2.325668706706138</v>
+        <v>2.246006354900591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/matches/south-east-melbourne-phoenix-v-illawarra-hawks-men-04-10-2026</t>
+          <t>/matches/cairns-taipans-v-brisbane-bullets-men-08-10-2026</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,89 +1370,89 @@
         </is>
       </c>
       <c r="E7" s="2">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="F7" s="2">
         <v>46296</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>south east melbourne phoenix</t>
+          <t>cairns taipans</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>illawarra hawks</t>
+          <t>brisbane bullets</t>
         </is>
       </c>
       <c r="I7">
-        <v>4.614123382190286</v>
+        <v>1.637757056815815</v>
       </c>
       <c r="J7">
-        <v>0.4105067446507376</v>
+        <v>-9.537703593624418</v>
       </c>
       <c r="K7">
-        <v>0.4105067446507376</v>
+        <v>-9.537703593624418</v>
       </c>
       <c r="L7">
-        <v>-5.143505324296937</v>
+        <v>-7.623537629893447</v>
       </c>
       <c r="M7">
-        <v>-3.885151168476717</v>
+        <v>3.606217570975567</v>
       </c>
       <c r="N7">
-        <v>-1.25835415582022</v>
+        <v>-11.22975520086901</v>
       </c>
       <c r="O7">
-        <v>-4.203616637539549</v>
+        <v>-11.17546065044023</v>
       </c>
       <c r="P7">
-        <v>-4.203616637539549</v>
+        <v>-11.17546065044023</v>
       </c>
       <c r="Q7">
         <v>0.2</v>
       </c>
       <c r="R7">
-        <v>0.1147008321225729</v>
+        <v>0.0880190655015525</v>
       </c>
       <c r="S7">
-        <v>189.6986029213629</v>
+        <v>178.0918631185139</v>
       </c>
       <c r="T7">
-        <v>86.52956592639438</v>
+        <v>83.17537557593369</v>
       </c>
       <c r="U7">
-        <v>86.87030465523057</v>
+        <v>93.33077548786395</v>
       </c>
       <c r="V7">
-        <v>173.399870581625</v>
+        <v>176.5061510637976</v>
       </c>
       <c r="W7">
-        <v>-16.29873233973797</v>
+        <v>-1.585712054716225</v>
       </c>
       <c r="X7">
-        <v>-16.29873233973797</v>
+        <v>-1.585712054716225</v>
       </c>
       <c r="Y7">
         <v>0.3</v>
       </c>
       <c r="Z7">
-        <v>0.1720512481838594</v>
+        <v>0.1320285982523288</v>
       </c>
       <c r="AA7">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AB7">
         <v>1</v>
       </c>
       <c r="AC7">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AD7">
-        <v>0.8573504160612865</v>
+        <v>0.8440095327507763</v>
       </c>
       <c r="AE7">
-        <v>0.5735041606128645</v>
+        <v>0.4400953275077625</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1474,32 +1474,488 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Dan Grida;Will Hickey;Amarco Doyle</t>
+          <t>Rio Bruton;Josh Duach;Billy McRae</t>
         </is>
       </c>
       <c r="AL7">
-        <v>4.131965055940208</v>
+        <v>0.6541034538146935</v>
       </c>
       <c r="AM7">
-        <v>-4.131965055940208</v>
+        <v>-0.6541034538146935</v>
       </c>
       <c r="AN7">
-        <v>186.8943856784964</v>
+        <v>177.8825037786979</v>
       </c>
       <c r="AO7">
-        <v>95.5131753672183</v>
+        <v>89.26830361625628</v>
       </c>
       <c r="AP7">
-        <v>91.38121031127808</v>
+        <v>88.61420016244159</v>
       </c>
       <c r="AQ7">
-        <v>0.6347010957155231</v>
+        <v>0.5217350299412284</v>
       </c>
       <c r="AR7">
-        <v>1.575544782812548</v>
+        <v>1.916681730403738</v>
       </c>
       <c r="AS7">
-        <v>2.73748425815493</v>
+        <v>2.090891164111633</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>/matches/illawarra-hawks-v-tasmania-jackjumpers-men-09-10-2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E8" s="2">
+        <v>46304</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46296</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>illawarra hawks</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tasmania jackjumpers</t>
+        </is>
+      </c>
+      <c r="I8">
+        <v>0.561711130531549</v>
+      </c>
+      <c r="J8">
+        <v>3.971708484556455</v>
+      </c>
+      <c r="K8">
+        <v>3.971708484556455</v>
+      </c>
+      <c r="L8">
+        <v>-3.921718730195348</v>
+      </c>
+      <c r="M8">
+        <v>-6.201250578537921</v>
+      </c>
+      <c r="N8">
+        <v>2.279531848342573</v>
+      </c>
+      <c r="O8">
+        <v>3.409997354024906</v>
+      </c>
+      <c r="P8">
+        <v>3.409997354024906</v>
+      </c>
+      <c r="Q8">
+        <v>0.2</v>
+      </c>
+      <c r="R8">
+        <v>0.1147008321225729</v>
+      </c>
+      <c r="S8">
+        <v>184.8055511718787</v>
+      </c>
+      <c r="T8">
+        <v>88.30212996060506</v>
+      </c>
+      <c r="U8">
+        <v>88.84623736566319</v>
+      </c>
+      <c r="V8">
+        <v>177.1483673262682</v>
+      </c>
+      <c r="W8">
+        <v>-7.657183845610433</v>
+      </c>
+      <c r="X8">
+        <v>-7.657183845610433</v>
+      </c>
+      <c r="Y8">
+        <v>0.3</v>
+      </c>
+      <c r="Z8">
+        <v>0.1720512481838594</v>
+      </c>
+      <c r="AA8">
+        <v>0.8573504160612865</v>
+      </c>
+      <c r="AB8">
+        <v>0.8573504160612865</v>
+      </c>
+      <c r="AC8">
+        <v>0.9550161660653202</v>
+      </c>
+      <c r="AD8">
+        <v>0.8573504160612865</v>
+      </c>
+      <c r="AE8">
+        <v>0.5735041606128645</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>true_home</t>
+        </is>
+      </c>
+      <c r="AG8">
+        <v>1.047658555274772</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>named_modelled_minutes/named_modelled_minutes</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Dan Grida;Will Hickey;Amarco Doyle;Nick Stoddart</t>
+        </is>
+      </c>
+      <c r="AL8">
+        <v>0.9528406645739774</v>
+      </c>
+      <c r="AM8">
+        <v>-0.9528406645739774</v>
+      </c>
+      <c r="AN8">
+        <v>183.4881231336681</v>
+      </c>
+      <c r="AO8">
+        <v>92.22048189912105</v>
+      </c>
+      <c r="AP8">
+        <v>91.26764123454707</v>
+      </c>
+      <c r="AQ8">
+        <v>0.5316441133250711</v>
+      </c>
+      <c r="AR8">
+        <v>1.88095753331243</v>
+      </c>
+      <c r="AS8">
+        <v>2.135128496194324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>/matches/perth-wildcats-v-nz-breakers-men-10-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E9" s="2">
+        <v>46305</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46296</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>perth wildcats</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>new zealand breakers</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>1.887227250972472</v>
+      </c>
+      <c r="J9">
+        <v>1.638284800951612</v>
+      </c>
+      <c r="K9">
+        <v>1.638284800951612</v>
+      </c>
+      <c r="L9">
+        <v>-0.8680524058389517</v>
+      </c>
+      <c r="M9">
+        <v>-0.814035553728732</v>
+      </c>
+      <c r="N9">
+        <v>-0.05401685211021967</v>
+      </c>
+      <c r="O9">
+        <v>-0.2489424500208606</v>
+      </c>
+      <c r="P9">
+        <v>-0.2489424500208606</v>
+      </c>
+      <c r="Q9">
+        <v>0.2</v>
+      </c>
+      <c r="R9">
+        <v>0.1104751692245827</v>
+      </c>
+      <c r="S9">
+        <v>185.3959258446141</v>
+      </c>
+      <c r="T9">
+        <v>88.93611463638582</v>
+      </c>
+      <c r="U9">
+        <v>93.01998361659021</v>
+      </c>
+      <c r="V9">
+        <v>181.956098252976</v>
+      </c>
+      <c r="W9">
+        <v>-3.43982759163805</v>
+      </c>
+      <c r="X9">
+        <v>-3.43982759163805</v>
+      </c>
+      <c r="Y9">
+        <v>0.3</v>
+      </c>
+      <c r="Z9">
+        <v>0.1657127538368741</v>
+      </c>
+      <c r="AA9">
+        <v>0.8552375846122914</v>
+      </c>
+      <c r="AB9">
+        <v>0.9496485891115073</v>
+      </c>
+      <c r="AC9">
+        <v>0.8552375846122914</v>
+      </c>
+      <c r="AD9">
+        <v>0.8552375846122914</v>
+      </c>
+      <c r="AE9">
+        <v>0.5523758461229135</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>true_home</t>
+        </is>
+      </c>
+      <c r="AG9">
+        <v>1.047658555274772</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>named_modelled_minutes/named_modelled_minutes</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Jo Lual-Acuil Jr.;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
+        </is>
+      </c>
+      <c r="AL9">
+        <v>1.859725291679236</v>
+      </c>
+      <c r="AM9">
+        <v>-1.859725291679236</v>
+      </c>
+      <c r="AN9">
+        <v>184.8259025416797</v>
+      </c>
+      <c r="AO9">
+        <v>93.34281391667946</v>
+      </c>
+      <c r="AP9">
+        <v>91.48308862500022</v>
+      </c>
+      <c r="AQ9">
+        <v>0.561580317651537</v>
+      </c>
+      <c r="AR9">
+        <v>1.780689188292572</v>
+      </c>
+      <c r="AS9">
+        <v>2.280919493950055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>/matches/south-east-melbourne-phoenix-v-melbourne-united-men-10-10-2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E10" s="2">
+        <v>46305</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46296</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>south east melbourne phoenix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>melbourne united</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>0.9169405915865951</v>
+      </c>
+      <c r="J10">
+        <v>-6.532553257643139</v>
+      </c>
+      <c r="K10">
+        <v>-6.532553257643139</v>
+      </c>
+      <c r="L10">
+        <v>-5.057457712711317</v>
+      </c>
+      <c r="M10">
+        <v>2.480849753378603</v>
+      </c>
+      <c r="N10">
+        <v>-7.53830746608992</v>
+      </c>
+      <c r="O10">
+        <v>-7.449493849229734</v>
+      </c>
+      <c r="P10">
+        <v>-7.449493849229734</v>
+      </c>
+      <c r="Q10">
+        <v>0.2</v>
+      </c>
+      <c r="R10">
+        <v>0.1831611045231239</v>
+      </c>
+      <c r="S10">
+        <v>180.5410249378599</v>
+      </c>
+      <c r="T10">
+        <v>86.14388282805488</v>
+      </c>
+      <c r="U10">
+        <v>92.66793534247309</v>
+      </c>
+      <c r="V10">
+        <v>178.811818170528</v>
+      </c>
+      <c r="W10">
+        <v>-1.729206767331931</v>
+      </c>
+      <c r="X10">
+        <v>-1.729206767331931</v>
+      </c>
+      <c r="Y10">
+        <v>0.3</v>
+      </c>
+      <c r="Z10">
+        <v>0.2747416567846859</v>
+      </c>
+      <c r="AA10">
+        <v>0.891580552261562</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>0.891580552261562</v>
+      </c>
+      <c r="AD10">
+        <v>0.891580552261562</v>
+      </c>
+      <c r="AE10">
+        <v>0.9158055226156194</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>same_city_shared</t>
+        </is>
+      </c>
+      <c r="AG10">
+        <v>0.3611111106597222</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>named_modelled_minutes/named_modelled_minutes</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Jai Fa'ale;Will Hynes</t>
+        </is>
+      </c>
+      <c r="AL10">
+        <v>-0.4475169299765407</v>
+      </c>
+      <c r="AM10">
+        <v>0.4475169299765407</v>
+      </c>
+      <c r="AN10">
+        <v>180.0659398056798</v>
+      </c>
+      <c r="AO10">
+        <v>89.80921143785166</v>
+      </c>
+      <c r="AP10">
+        <v>90.25672836782819</v>
+      </c>
+      <c r="AQ10">
+        <v>0.4851256625056887</v>
+      </c>
+      <c r="AR10">
+        <v>2.061321585906154</v>
+      </c>
+      <c r="AS10">
+        <v>1.942221484307419</v>
       </c>
     </row>
   </sheetData>

--- a/files/NBL_upcoming_projections_v4_shadow.xlsx
+++ b/files/NBL_upcoming_projections_v4_shadow.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AS8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
@@ -593,106 +593,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>/matches/brisbane-bullets-v-tasmania-jackjumpers-men-03-10-2026</t>
+          <t>/matches/adelaide-36ers-v-melbourne-united-men-07-10-2026</t>
         </is>
       </c>
       <c r="B2" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <v>46302</v>
+      </c>
+      <c r="F2" s="2">
         <v>46298</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E2" s="2">
-        <v>46298</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46296</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>brisbane bullets</t>
+          <t>adelaide 36ers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>tasmania jackjumpers</t>
+          <t>melbourne united</t>
         </is>
       </c>
       <c r="I2">
-        <v>-4.892729581328908</v>
+        <v>0.3152112879671591</v>
       </c>
       <c r="J2">
-        <v>11.46109669507977</v>
+        <v>9.222305667031687</v>
       </c>
       <c r="K2">
-        <v>11.46109669507977</v>
+        <v>9.222305667031687</v>
       </c>
       <c r="L2">
-        <v>3.81750707863487</v>
+        <v>6.232597404000669</v>
       </c>
       <c r="M2">
-        <v>-5.976619827034386</v>
+        <v>-1.225259175162939</v>
       </c>
       <c r="N2">
-        <v>9.794126905669255</v>
+        <v>7.457856579163607</v>
       </c>
       <c r="O2">
-        <v>16.35382627640868</v>
+        <v>8.907094379064528</v>
       </c>
       <c r="P2">
-        <v>15</v>
+        <v>8.907094379064528</v>
       </c>
       <c r="Q2">
         <v>0.2</v>
       </c>
       <c r="R2">
-        <v>0.0880190655015525</v>
+        <v>0.1904883149949986</v>
       </c>
       <c r="S2">
-        <v>177.6573858471099</v>
+        <v>182.3475305157114</v>
       </c>
       <c r="T2">
-        <v>93.10222085897135</v>
+        <v>94.8009868419291</v>
       </c>
       <c r="U2">
-        <v>87.27444765667697</v>
+        <v>91.73986458883927</v>
       </c>
       <c r="V2">
-        <v>180.3766685156483</v>
+        <v>186.5408514307684</v>
       </c>
       <c r="W2">
-        <v>2.719282668538369</v>
+        <v>4.193320915057029</v>
       </c>
       <c r="X2">
-        <v>2.719282668538369</v>
+        <v>4.193320915057029</v>
       </c>
       <c r="Y2">
         <v>0.3</v>
       </c>
       <c r="Z2">
-        <v>0.1320285982523288</v>
+        <v>0.2857324724924979</v>
       </c>
       <c r="AA2">
-        <v>0.8440095327507763</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AB2">
-        <v>0.8440095327507763</v>
+        <v>0.8963693281997769</v>
       </c>
       <c r="AC2">
-        <v>0.9550161660653202</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AD2">
-        <v>0.8440095327507763</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AE2">
-        <v>0.4400953275077625</v>
+        <v>0.9524415749749928</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -714,137 +714,137 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Rio Bruton;Josh Duach;Billy McRae;Nick Stoddart</t>
+          <t>John Jenkins III;Harvey White;Jai Fa'ale;Will Hynes</t>
         </is>
       </c>
       <c r="AL2">
-        <v>-3.57244359880562</v>
+        <v>2.011908687736584</v>
       </c>
       <c r="AM2">
-        <v>3.57244359880562</v>
+        <v>-2.011908687736584</v>
       </c>
       <c r="AN2">
-        <v>178.0164089260889</v>
+        <v>183.5456984687251</v>
       </c>
       <c r="AO2">
-        <v>87.22198266364164</v>
+        <v>92.77880357823085</v>
       </c>
       <c r="AP2">
-        <v>90.79442626244726</v>
+        <v>90.76689489049426</v>
       </c>
       <c r="AQ2">
-        <v>0.3829646850905365</v>
+        <v>0.566574246152552</v>
       </c>
       <c r="AR2">
-        <v>2.611206826456049</v>
+        <v>1.76499374405159</v>
       </c>
       <c r="AS2">
-        <v>1.620652782485762</v>
+        <v>2.307200232388517</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/matches/melbourne-united-v-cairns-taipans-men-03-10-2026</t>
+          <t>/matches/cairns-taipans-v-brisbane-bullets-men-08-10-2026</t>
         </is>
       </c>
       <c r="B3" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
+        </is>
+      </c>
+      <c r="E3" s="2">
+        <v>46303</v>
+      </c>
+      <c r="F3" s="2">
         <v>46298</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E3" s="2">
-        <v>46298</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46296</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>melbourne united</t>
+          <t>cairns taipans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cairns taipans</t>
+          <t>brisbane bullets</t>
         </is>
       </c>
       <c r="I3">
-        <v>8.873042196210363</v>
+        <v>2.449750596316164</v>
       </c>
       <c r="J3">
-        <v>11.50063075049427</v>
+        <v>-3.254878729974809</v>
       </c>
       <c r="K3">
-        <v>11.50063075049427</v>
+        <v>-3.254878729974809</v>
       </c>
       <c r="L3">
-        <v>2.57555777695428</v>
+        <v>-5.231057953019635</v>
       </c>
       <c r="M3">
-        <v>-7.25810318412947</v>
+        <v>-0.2116148009474413</v>
       </c>
       <c r="N3">
-        <v>9.833660961083751</v>
+        <v>-5.019443152072194</v>
       </c>
       <c r="O3">
-        <v>2.627588554283903</v>
+        <v>-5.704629326290974</v>
       </c>
       <c r="P3">
-        <v>2.627588554283903</v>
+        <v>-5.704629326290974</v>
       </c>
       <c r="Q3">
         <v>0.2</v>
       </c>
       <c r="R3">
-        <v>0.1831611045231239</v>
+        <v>0.1285579641847312</v>
       </c>
       <c r="S3">
-        <v>176.2359142406692</v>
+        <v>180.3023945102344</v>
       </c>
       <c r="T3">
-        <v>94.51175139949508</v>
+        <v>86.20439047486066</v>
       </c>
       <c r="U3">
-        <v>84.4885972531078</v>
+        <v>88.81704611178657</v>
       </c>
       <c r="V3">
-        <v>179.0003486526029</v>
+        <v>175.0214365866472</v>
       </c>
       <c r="W3">
-        <v>2.764434411933678</v>
+        <v>-5.280957923587181</v>
       </c>
       <c r="X3">
-        <v>2.764434411933678</v>
+        <v>-5.280957923587181</v>
       </c>
       <c r="Y3">
         <v>0.3</v>
       </c>
       <c r="Z3">
-        <v>0.2747416567846859</v>
+        <v>0.1928369462770969</v>
       </c>
       <c r="AA3">
-        <v>0.891580552261562</v>
+        <v>0.8642789820923656</v>
       </c>
       <c r="AB3">
-        <v>0.891580552261562</v>
+        <v>1</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0.8642789820923656</v>
       </c>
       <c r="AD3">
-        <v>0.891580552261562</v>
+        <v>0.8642789820923656</v>
       </c>
       <c r="AE3">
-        <v>0.9158055226156194</v>
+        <v>0.6427898209236561</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -866,42 +866,42 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Jai Fa'ale;Will Hynes</t>
+          <t>Rio Bruton;Josh Duach;Billy McRae</t>
         </is>
       </c>
       <c r="AL3">
-        <v>9.354314218045321</v>
+        <v>1.716375063699682</v>
       </c>
       <c r="AM3">
-        <v>-9.354314218045321</v>
+        <v>-1.716375063699682</v>
       </c>
       <c r="AN3">
-        <v>176.9954195310765</v>
+        <v>179.284030710832</v>
       </c>
       <c r="AO3">
-        <v>93.17486687456089</v>
+        <v>90.50020288726584</v>
       </c>
       <c r="AP3">
-        <v>83.82055265651557</v>
+        <v>88.78382782356617</v>
       </c>
       <c r="AQ3">
-        <v>0.7821650904627131</v>
+        <v>0.5568672515994699</v>
       </c>
       <c r="AR3">
-        <v>1.278502469866585</v>
+        <v>1.795760115409437</v>
       </c>
       <c r="AS3">
-        <v>4.590632429504278</v>
+        <v>2.256660117333824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/matches/adelaide-36ers-v-nz-breakers-men-04-10-2026</t>
+          <t>/matches/illawarra-hawks-v-tasmania-jackjumpers-men-09-10-2026</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,89 +914,89 @@
         </is>
       </c>
       <c r="E4" s="2">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="F4" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>adelaide 36ers</t>
+          <t>illawarra hawks</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>new zealand breakers</t>
+          <t>tasmania jackjumpers</t>
         </is>
       </c>
       <c r="I4">
-        <v>1.11091053240331</v>
+        <v>1.534316430712551</v>
       </c>
       <c r="J4">
-        <v>10.21768672024316</v>
+        <v>6.27265269965294</v>
       </c>
       <c r="K4">
-        <v>10.21768672024316</v>
+        <v>6.27265269965294</v>
       </c>
       <c r="L4">
-        <v>7.72462376534731</v>
+        <v>-0.3428380310039436</v>
       </c>
       <c r="M4">
-        <v>-0.8242020544248913</v>
+        <v>-4.850811025509802</v>
       </c>
       <c r="N4">
-        <v>8.548825819772201</v>
+        <v>4.507972994505859</v>
       </c>
       <c r="O4">
-        <v>9.106776187839849</v>
+        <v>4.738336268940389</v>
       </c>
       <c r="P4">
-        <v>9.106776187839849</v>
+        <v>4.738336268940389</v>
       </c>
       <c r="Q4">
         <v>0.2</v>
       </c>
       <c r="R4">
-        <v>0.1104751692245827</v>
+        <v>0.1189695550351289</v>
       </c>
       <c r="S4">
-        <v>187.7010393664982</v>
+        <v>186.7244048901792</v>
       </c>
       <c r="T4">
-        <v>96.26215855282854</v>
+        <v>92.41303955426241</v>
       </c>
       <c r="U4">
-        <v>90.79262213091847</v>
+        <v>89.87024531859977</v>
       </c>
       <c r="V4">
-        <v>187.054780683747</v>
+        <v>182.2832848728622</v>
       </c>
       <c r="W4">
-        <v>-0.6462586827511814</v>
+        <v>-4.441120017317076</v>
       </c>
       <c r="X4">
-        <v>-0.6462586827511814</v>
+        <v>-4.441120017317076</v>
       </c>
       <c r="Y4">
         <v>0.3</v>
       </c>
       <c r="Z4">
-        <v>0.1657127538368741</v>
+        <v>0.1784543325526933</v>
       </c>
       <c r="AA4">
-        <v>0.8552375846122914</v>
+        <v>0.8594847775175645</v>
       </c>
       <c r="AB4">
-        <v>0.8903358464701852</v>
+        <v>0.8594847775175645</v>
       </c>
       <c r="AC4">
-        <v>0.8552375846122914</v>
+        <v>0.9574788501572397</v>
       </c>
       <c r="AD4">
-        <v>0.8552375846122914</v>
+        <v>0.8594847775175645</v>
       </c>
       <c r="AE4">
-        <v>0.5523758461229135</v>
+        <v>0.5948477751756444</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1018,42 +1018,42 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>John Jenkins III;Harvey White;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
+          <t>Dan Grida;Will Hickey;Amarco Doyle;Nick Stoddart</t>
         </is>
       </c>
       <c r="AL4">
-        <v>2.116983172845317</v>
+        <v>2.098034188235201</v>
       </c>
       <c r="AM4">
-        <v>-2.116983172845317</v>
+        <v>-2.098034188235201</v>
       </c>
       <c r="AN4">
-        <v>187.5939460604885</v>
+        <v>185.9318677817025</v>
       </c>
       <c r="AO4">
-        <v>94.85546461666692</v>
+        <v>94.01495098496886</v>
       </c>
       <c r="AP4">
-        <v>92.7384814438216</v>
+        <v>91.91691679673366</v>
       </c>
       <c r="AQ4">
-        <v>0.5700161432638842</v>
+        <v>0.5693958216066768</v>
       </c>
       <c r="AR4">
-        <v>1.754336279449999</v>
+        <v>1.756247520711125</v>
       </c>
       <c r="AS4">
-        <v>2.325668706706138</v>
+        <v>2.322318384673403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>/matches/south-east-melbourne-phoenix-v-illawarra-hawks-men-04-10-2026</t>
+          <t>/matches/perth-wildcats-v-nz-breakers-men-10-10-2026</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,89 +1066,89 @@
         </is>
       </c>
       <c r="E5" s="2">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="F5" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>south east melbourne phoenix</t>
+          <t>perth wildcats</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>illawarra hawks</t>
+          <t>new zealand breakers</t>
         </is>
       </c>
       <c r="I5">
-        <v>4.614123382190286</v>
+        <v>1.843200937278539</v>
       </c>
       <c r="J5">
-        <v>0.4105067446507376</v>
+        <v>3.203586517674395</v>
       </c>
       <c r="K5">
-        <v>0.4105067446507376</v>
+        <v>3.203586517674395</v>
       </c>
       <c r="L5">
-        <v>-5.143505324296937</v>
+        <v>0.3725635155479431</v>
       </c>
       <c r="M5">
-        <v>-3.885151168476717</v>
+        <v>-1.066228064280848</v>
       </c>
       <c r="N5">
-        <v>-1.25835415582022</v>
+        <v>1.438791579828791</v>
       </c>
       <c r="O5">
-        <v>-4.203616637539549</v>
+        <v>1.360385580395857</v>
       </c>
       <c r="P5">
-        <v>-4.203616637539549</v>
+        <v>1.360385580395857</v>
       </c>
       <c r="Q5">
         <v>0.2</v>
       </c>
       <c r="R5">
-        <v>0.1147008321225729</v>
+        <v>0.1104751692245827</v>
       </c>
       <c r="S5">
-        <v>189.6986029213629</v>
+        <v>185.6518701464311</v>
       </c>
       <c r="T5">
-        <v>86.52956592639438</v>
+        <v>90.31927977305655</v>
       </c>
       <c r="U5">
-        <v>86.87030465523057</v>
+        <v>93.37344846800328</v>
       </c>
       <c r="V5">
-        <v>173.399870581625</v>
+        <v>183.6927282410598</v>
       </c>
       <c r="W5">
-        <v>-16.29873233973797</v>
+        <v>-1.95914190537124</v>
       </c>
       <c r="X5">
-        <v>-16.29873233973797</v>
+        <v>-1.95914190537124</v>
       </c>
       <c r="Y5">
         <v>0.3</v>
       </c>
       <c r="Z5">
-        <v>0.1720512481838594</v>
+        <v>0.1657127538368741</v>
       </c>
       <c r="AA5">
-        <v>0.8573504160612865</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>0.9475849015396934</v>
       </c>
       <c r="AC5">
-        <v>0.8573504160612865</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AD5">
-        <v>0.8573504160612865</v>
+        <v>0.8552375846122914</v>
       </c>
       <c r="AE5">
-        <v>0.5735041606128645</v>
+        <v>0.5523758461229135</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1165,47 +1165,47 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
+          <t>league_last5;neutral_fallback</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Dan Grida;Will Hickey;Amarco Doyle</t>
+          <t>Jo Lual-Acuil Jr.;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
         </is>
       </c>
       <c r="AL5">
-        <v>4.131965055940208</v>
+        <v>1.993489764483453</v>
       </c>
       <c r="AM5">
-        <v>-4.131965055940208</v>
+        <v>-1.993489764483453</v>
       </c>
       <c r="AN5">
-        <v>186.8943856784964</v>
+        <v>185.3272153461348</v>
       </c>
       <c r="AO5">
-        <v>95.5131753672183</v>
+        <v>93.66035255530912</v>
       </c>
       <c r="AP5">
-        <v>91.38121031127808</v>
+        <v>91.66686279082566</v>
       </c>
       <c r="AQ5">
-        <v>0.6347010957155231</v>
+        <v>0.5659703742032898</v>
       </c>
       <c r="AR5">
-        <v>1.575544782812548</v>
+        <v>1.766876934870821</v>
       </c>
       <c r="AS5">
-        <v>2.73748425815493</v>
+        <v>2.3039901899885</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>/matches/adelaide-36ers-v-melbourne-united-men-07-10-2026</t>
+          <t>/matches/south-east-melbourne-phoenix-v-melbourne-united-men-10-10-2026</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,14 +1218,14 @@
         </is>
       </c>
       <c r="E6" s="2">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="F6" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>adelaide 36ers</t>
+          <t>south east melbourne phoenix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1234,81 +1234,81 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.4771933121615604</v>
+        <v>1.519069327488239</v>
       </c>
       <c r="J6">
-        <v>6.982526168355089</v>
+        <v>-1.034079430326075</v>
       </c>
       <c r="K6">
-        <v>6.982526168355089</v>
+        <v>-1.034079430326075</v>
       </c>
       <c r="L6">
-        <v>7.773458410712558</v>
+        <v>-3.337960560714978</v>
       </c>
       <c r="M6">
-        <v>2.482858807531738</v>
+        <v>-1.225633637158348</v>
       </c>
       <c r="N6">
-        <v>5.290599603180819</v>
+        <v>-2.11232692355663</v>
       </c>
       <c r="O6">
-        <v>6.505332856193529</v>
+        <v>-2.553148757814314</v>
       </c>
       <c r="P6">
-        <v>6.505332856193529</v>
+        <v>-2.553148757814314</v>
       </c>
       <c r="Q6">
         <v>0.2</v>
       </c>
       <c r="R6">
-        <v>0.1806716929403703</v>
+        <v>0.1904883149949986</v>
       </c>
       <c r="S6">
-        <v>180.4772482411747</v>
+        <v>181.5873769284743</v>
       </c>
       <c r="T6">
-        <v>94.76342739130703</v>
+        <v>89.00523615776068</v>
       </c>
       <c r="U6">
-        <v>92.38807047670807</v>
+        <v>93.01489012844452</v>
       </c>
       <c r="V6">
-        <v>187.1514978680151</v>
+        <v>182.0201262862052</v>
       </c>
       <c r="W6">
-        <v>6.674249626840435</v>
+        <v>0.4327493577309269</v>
       </c>
       <c r="X6">
-        <v>6.674249626840435</v>
+        <v>0.4327493577309269</v>
       </c>
       <c r="Y6">
         <v>0.3</v>
       </c>
       <c r="Z6">
-        <v>0.2710075394105554</v>
+        <v>0.2857324724924979</v>
       </c>
       <c r="AA6">
-        <v>0.8903358464701852</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AB6">
-        <v>0.8903358464701852</v>
+        <v>1</v>
       </c>
       <c r="AC6">
-        <v>0.891580552261562</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AD6">
-        <v>0.8903358464701852</v>
+        <v>0.8952441574974993</v>
       </c>
       <c r="AE6">
-        <v>0.9033584647018513</v>
+        <v>0.9524415749749928</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>true_home</t>
+          <t>same_city_shared</t>
         </is>
       </c>
       <c r="AG6">
-        <v>1.047658555274772</v>
+        <v>0.3611111106597222</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1317,47 +1317,47 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
+          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>John Jenkins III;Harvey White;Jai Fa'ale;Will Hynes</t>
+          <t>Jai Fa'ale;Will Hynes</t>
         </is>
       </c>
       <c r="AL6">
-        <v>1.652522812430659</v>
+        <v>1.032724322680617</v>
       </c>
       <c r="AM6">
-        <v>-1.652522812430659</v>
+        <v>-1.032724322680617</v>
       </c>
       <c r="AN6">
-        <v>182.2860202099565</v>
+        <v>181.7110274724283</v>
       </c>
       <c r="AO6">
-        <v>91.96927151119358</v>
+        <v>91.37187589755445</v>
       </c>
       <c r="AP6">
-        <v>90.31674869876294</v>
+        <v>90.33915157487382</v>
       </c>
       <c r="AQ6">
-        <v>0.5547652846938359</v>
+        <v>0.534290782684946</v>
       </c>
       <c r="AR6">
-        <v>1.802564125027903</v>
+        <v>1.871639999055847</v>
       </c>
       <c r="AS6">
-        <v>2.246006354900591</v>
+        <v>2.147262632604277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>/matches/cairns-taipans-v-brisbane-bullets-men-08-10-2026</t>
+          <t>/matches/illawarra-hawks-v-cairns-taipans-men-11-10-2026</t>
         </is>
       </c>
       <c r="B7" s="2">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,89 +1370,89 @@
         </is>
       </c>
       <c r="E7" s="2">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="F7" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>illawarra hawks</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>cairns taipans</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>brisbane bullets</t>
-        </is>
-      </c>
       <c r="I7">
-        <v>1.637757056815815</v>
+        <v>6.225714600747253</v>
       </c>
       <c r="J7">
-        <v>-9.537703593624418</v>
+        <v>6.67318180418299</v>
       </c>
       <c r="K7">
-        <v>-9.537703593624418</v>
+        <v>6.67318180418299</v>
       </c>
       <c r="L7">
-        <v>-7.623537629893447</v>
+        <v>-0.3438396186559749</v>
       </c>
       <c r="M7">
-        <v>3.606217570975567</v>
+        <v>-5.265899627300536</v>
       </c>
       <c r="N7">
-        <v>-11.22975520086901</v>
+        <v>4.922060008644561</v>
       </c>
       <c r="O7">
-        <v>-11.17546065044023</v>
+        <v>0.4474672034357372</v>
       </c>
       <c r="P7">
-        <v>-11.17546065044023</v>
+        <v>0.4474672034357372</v>
       </c>
       <c r="Q7">
         <v>0.2</v>
       </c>
       <c r="R7">
-        <v>0.0880190655015525</v>
+        <v>0.1189695550351289</v>
       </c>
       <c r="S7">
-        <v>178.0918631185139</v>
+        <v>187.2148202205194</v>
       </c>
       <c r="T7">
-        <v>83.17537557593369</v>
+        <v>91.68373793190466</v>
       </c>
       <c r="U7">
-        <v>93.33077548786395</v>
+        <v>87.01017899886585</v>
       </c>
       <c r="V7">
-        <v>176.5061510637976</v>
+        <v>178.6939169307705</v>
       </c>
       <c r="W7">
-        <v>-1.585712054716225</v>
+        <v>-8.520903289748901</v>
       </c>
       <c r="X7">
-        <v>-1.585712054716225</v>
+        <v>-8.520903289748901</v>
       </c>
       <c r="Y7">
         <v>0.3</v>
       </c>
       <c r="Z7">
-        <v>0.1320285982523288</v>
+        <v>0.1784543325526933</v>
       </c>
       <c r="AA7">
-        <v>0.8440095327507763</v>
+        <v>0.8594847775175645</v>
       </c>
       <c r="AB7">
+        <v>0.8594847775175645</v>
+      </c>
+      <c r="AC7">
         <v>1</v>
       </c>
-      <c r="AC7">
-        <v>0.8440095327507763</v>
-      </c>
       <c r="AD7">
-        <v>0.8440095327507763</v>
+        <v>0.8594847775175645</v>
       </c>
       <c r="AE7">
-        <v>0.4400953275077625</v>
+        <v>0.5948477751756444</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
+          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Rio Bruton;Josh Duach;Billy McRae</t>
+          <t>Dan Grida;Will Hickey;Amarco Doyle</t>
         </is>
       </c>
       <c r="AL7">
-        <v>0.6541034538146935</v>
+        <v>6.278949574832816</v>
       </c>
       <c r="AM7">
-        <v>-0.6541034538146935</v>
+        <v>-6.278949574832816</v>
       </c>
       <c r="AN7">
-        <v>177.8825037786979</v>
+        <v>185.6942281112012</v>
       </c>
       <c r="AO7">
-        <v>89.26830361625628</v>
+        <v>95.98658884301702</v>
       </c>
       <c r="AP7">
-        <v>88.61420016244159</v>
+        <v>89.70763926818421</v>
       </c>
       <c r="AQ7">
-        <v>0.5217350299412284</v>
+        <v>0.6995983926989496</v>
       </c>
       <c r="AR7">
-        <v>1.916681730403738</v>
+        <v>1.429391505806845</v>
       </c>
       <c r="AS7">
-        <v>2.090891164111633</v>
+        <v>3.328876995647498</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>/matches/illawarra-hawks-v-tasmania-jackjumpers-men-09-10-2026</t>
+          <t>/matches/sydney-kings-v-adelaide-36ers-men-11-10-2026</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1522,89 +1522,89 @@
         </is>
       </c>
       <c r="E8" s="2">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="F8" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>illawarra hawks</t>
+          <t>sydney kings</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>tasmania jackjumpers</t>
+          <t>adelaide 36ers</t>
         </is>
       </c>
       <c r="I8">
-        <v>0.561711130531549</v>
+        <v>9.096122028452726</v>
       </c>
       <c r="J8">
-        <v>3.971708484556455</v>
+        <v>4.769316169555685</v>
       </c>
       <c r="K8">
-        <v>3.971708484556455</v>
+        <v>4.769316169555685</v>
       </c>
       <c r="L8">
-        <v>-3.921718730195348</v>
+        <v>9.243972978153819</v>
       </c>
       <c r="M8">
-        <v>-6.201250578537921</v>
+        <v>6.225778604136563</v>
       </c>
       <c r="N8">
-        <v>2.279531848342573</v>
+        <v>3.018194374017256</v>
       </c>
       <c r="O8">
-        <v>3.409997354024906</v>
+        <v>-4.326805858897041</v>
       </c>
       <c r="P8">
-        <v>3.409997354024906</v>
+        <v>-4.326805858897041</v>
       </c>
       <c r="Q8">
         <v>0.2</v>
       </c>
       <c r="R8">
-        <v>0.1147008321225729</v>
+        <v>0.1927386563995537</v>
       </c>
       <c r="S8">
-        <v>184.8055511718787</v>
+        <v>190.6183336157335</v>
       </c>
       <c r="T8">
-        <v>88.30212996060506</v>
+        <v>101.8367764907647</v>
       </c>
       <c r="U8">
-        <v>88.84623736566319</v>
+        <v>94.35527999543756</v>
       </c>
       <c r="V8">
-        <v>177.1483673262682</v>
+        <v>196.1920564862023</v>
       </c>
       <c r="W8">
-        <v>-7.657183845610433</v>
+        <v>5.573722870468828</v>
       </c>
       <c r="X8">
-        <v>-7.657183845610433</v>
+        <v>5.573722870468828</v>
       </c>
       <c r="Y8">
         <v>0.3</v>
       </c>
       <c r="Z8">
-        <v>0.1720512481838594</v>
+        <v>0.2891079845993306</v>
       </c>
       <c r="AA8">
-        <v>0.8573504160612865</v>
+        <v>0.8963693281997769</v>
       </c>
       <c r="AB8">
-        <v>0.8573504160612865</v>
+        <v>0.9462486002239642</v>
       </c>
       <c r="AC8">
-        <v>0.9550161660653202</v>
+        <v>0.8963693281997769</v>
       </c>
       <c r="AD8">
-        <v>0.8573504160612865</v>
+        <v>0.8963693281997769</v>
       </c>
       <c r="AE8">
-        <v>0.5735041606128645</v>
+        <v>0.9636932819977686</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1626,336 +1626,32 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Dan Grida;Will Hickey;Amarco Doyle;Nick Stoddart</t>
+          <t>Lachlan Bofinger;John Jenkins III;Harvey White</t>
         </is>
       </c>
       <c r="AL8">
-        <v>0.9528406645739774</v>
+        <v>8.262179280707192</v>
       </c>
       <c r="AM8">
-        <v>-0.9528406645739774</v>
+        <v>-8.262179280707192</v>
       </c>
       <c r="AN8">
-        <v>183.4881231336681</v>
+        <v>192.2297414015299</v>
       </c>
       <c r="AO8">
-        <v>92.22048189912105</v>
+        <v>100.2459603411185</v>
       </c>
       <c r="AP8">
-        <v>91.26764123454707</v>
+        <v>91.98378106041136</v>
       </c>
       <c r="AQ8">
-        <v>0.5316441133250711</v>
+        <v>0.7544357173179238</v>
       </c>
       <c r="AR8">
-        <v>1.88095753331243</v>
+        <v>1.325493977876705</v>
       </c>
       <c r="AS8">
-        <v>2.135128496194324</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>/matches/perth-wildcats-v-nz-breakers-men-10-10-2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <v>46305</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E9" s="2">
-        <v>46305</v>
-      </c>
-      <c r="F9" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>perth wildcats</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>new zealand breakers</t>
-        </is>
-      </c>
-      <c r="I9">
-        <v>1.887227250972472</v>
-      </c>
-      <c r="J9">
-        <v>1.638284800951612</v>
-      </c>
-      <c r="K9">
-        <v>1.638284800951612</v>
-      </c>
-      <c r="L9">
-        <v>-0.8680524058389517</v>
-      </c>
-      <c r="M9">
-        <v>-0.814035553728732</v>
-      </c>
-      <c r="N9">
-        <v>-0.05401685211021967</v>
-      </c>
-      <c r="O9">
-        <v>-0.2489424500208606</v>
-      </c>
-      <c r="P9">
-        <v>-0.2489424500208606</v>
-      </c>
-      <c r="Q9">
-        <v>0.2</v>
-      </c>
-      <c r="R9">
-        <v>0.1104751692245827</v>
-      </c>
-      <c r="S9">
-        <v>185.3959258446141</v>
-      </c>
-      <c r="T9">
-        <v>88.93611463638582</v>
-      </c>
-      <c r="U9">
-        <v>93.01998361659021</v>
-      </c>
-      <c r="V9">
-        <v>181.956098252976</v>
-      </c>
-      <c r="W9">
-        <v>-3.43982759163805</v>
-      </c>
-      <c r="X9">
-        <v>-3.43982759163805</v>
-      </c>
-      <c r="Y9">
-        <v>0.3</v>
-      </c>
-      <c r="Z9">
-        <v>0.1657127538368741</v>
-      </c>
-      <c r="AA9">
-        <v>0.8552375846122914</v>
-      </c>
-      <c r="AB9">
-        <v>0.9496485891115073</v>
-      </c>
-      <c r="AC9">
-        <v>0.8552375846122914</v>
-      </c>
-      <c r="AD9">
-        <v>0.8552375846122914</v>
-      </c>
-      <c r="AE9">
-        <v>0.5523758461229135</v>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>true_home</t>
-        </is>
-      </c>
-      <c r="AG9">
-        <v>1.047658555274772</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>named_modelled_minutes/named_modelled_minutes</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>league_last5;neutral_fallback;league_last5_returning_conservative</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>Jo Lual-Acuil Jr.;Aubrey Chunga;Kazlo Evans Jr.;Preston Le Gassick</t>
-        </is>
-      </c>
-      <c r="AL9">
-        <v>1.859725291679236</v>
-      </c>
-      <c r="AM9">
-        <v>-1.859725291679236</v>
-      </c>
-      <c r="AN9">
-        <v>184.8259025416797</v>
-      </c>
-      <c r="AO9">
-        <v>93.34281391667946</v>
-      </c>
-      <c r="AP9">
-        <v>91.48308862500022</v>
-      </c>
-      <c r="AQ9">
-        <v>0.561580317651537</v>
-      </c>
-      <c r="AR9">
-        <v>1.780689188292572</v>
-      </c>
-      <c r="AS9">
-        <v>2.280919493950055</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>/matches/south-east-melbourne-phoenix-v-melbourne-united-men-10-10-2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <v>46305</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nbl_lean_v4_player_ensemble_0.1.0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>player_only_d0975_l400_w20_sd0975_sl1600_tw30</t>
-        </is>
-      </c>
-      <c r="E10" s="2">
-        <v>46305</v>
-      </c>
-      <c r="F10" s="2">
-        <v>46296</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>south east melbourne phoenix</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>melbourne united</t>
-        </is>
-      </c>
-      <c r="I10">
-        <v>0.9169405915865951</v>
-      </c>
-      <c r="J10">
-        <v>-6.532553257643139</v>
-      </c>
-      <c r="K10">
-        <v>-6.532553257643139</v>
-      </c>
-      <c r="L10">
-        <v>-5.057457712711317</v>
-      </c>
-      <c r="M10">
-        <v>2.480849753378603</v>
-      </c>
-      <c r="N10">
-        <v>-7.53830746608992</v>
-      </c>
-      <c r="O10">
-        <v>-7.449493849229734</v>
-      </c>
-      <c r="P10">
-        <v>-7.449493849229734</v>
-      </c>
-      <c r="Q10">
-        <v>0.2</v>
-      </c>
-      <c r="R10">
-        <v>0.1831611045231239</v>
-      </c>
-      <c r="S10">
-        <v>180.5410249378599</v>
-      </c>
-      <c r="T10">
-        <v>86.14388282805488</v>
-      </c>
-      <c r="U10">
-        <v>92.66793534247309</v>
-      </c>
-      <c r="V10">
-        <v>178.811818170528</v>
-      </c>
-      <c r="W10">
-        <v>-1.729206767331931</v>
-      </c>
-      <c r="X10">
-        <v>-1.729206767331931</v>
-      </c>
-      <c r="Y10">
-        <v>0.3</v>
-      </c>
-      <c r="Z10">
-        <v>0.2747416567846859</v>
-      </c>
-      <c r="AA10">
-        <v>0.891580552261562</v>
-      </c>
-      <c r="AB10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>0.891580552261562</v>
-      </c>
-      <c r="AD10">
-        <v>0.891580552261562</v>
-      </c>
-      <c r="AE10">
-        <v>0.9158055226156194</v>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>same_city_shared</t>
-        </is>
-      </c>
-      <c r="AG10">
-        <v>0.3611111106597222</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>named_modelled_minutes/named_modelled_minutes</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>league_last5;league_last5_returning_conservative;neutral_fallback</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>Jai Fa'ale;Will Hynes</t>
-        </is>
-      </c>
-      <c r="AL10">
-        <v>-0.4475169299765407</v>
-      </c>
-      <c r="AM10">
-        <v>0.4475169299765407</v>
-      </c>
-      <c r="AN10">
-        <v>180.0659398056798</v>
-      </c>
-      <c r="AO10">
-        <v>89.80921143785166</v>
-      </c>
-      <c r="AP10">
-        <v>90.25672836782819</v>
-      </c>
-      <c r="AQ10">
-        <v>0.4851256625056887</v>
-      </c>
-      <c r="AR10">
-        <v>2.061321585906154</v>
-      </c>
-      <c r="AS10">
-        <v>1.942221484307419</v>
+        <v>4.072253460796114</v>
       </c>
     </row>
   </sheetData>
